--- a/tools/catalogue-excel-import/import-data/TMP.xlsx
+++ b/tools/catalogue-excel-import/import-data/TMP.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Lists of values" sheetId="1" state="visible" r:id="rId2"/>
@@ -1122,7 +1122,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12.71"/>
@@ -1293,12 +1293,12 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:R3"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="34.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="44.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="23.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="27.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="44.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="23.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="27.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="6" width="57.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="6" style="6" width="18.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="6" width="27"/>
@@ -1466,7 +1466,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="41.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.42"/>
@@ -1552,7 +1552,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.71"/>
@@ -1664,7 +1664,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.38"/>
@@ -1743,7 +1743,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="26.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.86"/>
@@ -1915,7 +1915,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="26.42"/>
@@ -2024,16 +2024,16 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AB108"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="44.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="32.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="21.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="21.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="46.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="6" width="57.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="6" style="6" width="18.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="6" width="13.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="6" width="19.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="6" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="6" width="19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="6" width="15.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="6" width="13.7"/>
@@ -3958,16 +3958,16 @@
       <formula1>'Lists of values'!$A$2:$A$1000</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="J3:J108" type="list">
-      <formula1>'Lists of values'!$C$2:$C$20</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G3:G108 I3:I108" type="list">
+      <formula1>'Lists of values'!$F$2:$F$20</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="F3:F108 H3:H108" type="list">
       <formula1>'Lists of values'!$E$2:$E$20</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G3:G108 I3:I108" type="list">
-      <formula1>'Lists of values'!$F$2:$F$20</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="J3:J108" type="list">
+      <formula1>'Lists of values'!$C$2:$C$20</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="M3:M108" type="list">
@@ -4015,7 +4015,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="0" width="24.71"/>
   </cols>
@@ -4120,11 +4120,11 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:W102"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="44.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="37.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="23.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="23.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="21.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="6" width="52.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="6" style="6" width="18.29"/>
@@ -5596,7 +5596,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="0" width="29.29"/>
   </cols>
